--- a/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N17_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G0/G0_DMSO_W0082F0003T0006Z000C1N17_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>41.79444023090733</v>
+        <v>6.791596537522442</v>
       </c>
       <c r="D2" t="n">
-        <v>25.29293168111907</v>
+        <v>4.110101398181849</v>
       </c>
       <c r="E2" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F2" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>45.73771103886569</v>
+        <v>7.432378043815675</v>
       </c>
       <c r="D3" t="n">
-        <v>18.98884823129391</v>
+        <v>3.08568783758526</v>
       </c>
       <c r="E3" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F3" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>32.19425318114321</v>
+        <v>5.231566141935772</v>
       </c>
       <c r="D4" t="n">
-        <v>15.54846929938707</v>
+        <v>2.5266262611504</v>
       </c>
       <c r="E4" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F4" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.55212647793087</v>
+        <v>4.152220552663766</v>
       </c>
       <c r="D5" t="n">
-        <v>22.58917961178058</v>
+        <v>3.670741686914344</v>
       </c>
       <c r="E5" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F5" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>33.66042653104213</v>
+        <v>5.469819311294347</v>
       </c>
       <c r="D6" t="n">
-        <v>15.38568062798336</v>
+        <v>2.500173102047296</v>
       </c>
       <c r="E6" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F6" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>21.55180689519486</v>
+        <v>3.502168620469166</v>
       </c>
       <c r="D7" t="n">
-        <v>19.92515987351822</v>
+        <v>3.237838479446711</v>
       </c>
       <c r="E7" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F7" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>23.11431826181721</v>
+        <v>3.756076717545297</v>
       </c>
       <c r="D8" t="n">
-        <v>19.37534059843953</v>
+        <v>3.148492847246424</v>
       </c>
       <c r="E8" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F8" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.18863390968916</v>
+        <v>3.118153010324489</v>
       </c>
       <c r="D9" t="n">
-        <v>15.9354021934258</v>
+        <v>2.589502856431693</v>
       </c>
       <c r="E9" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F9" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.12937978224483</v>
+        <v>3.271024214614784</v>
       </c>
       <c r="D10" t="n">
-        <v>21.66740415381873</v>
+        <v>3.520953174995544</v>
       </c>
       <c r="E10" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F10" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>18.06283305570138</v>
+        <v>2.935210371551474</v>
       </c>
       <c r="D11" t="n">
-        <v>15.5503416659816</v>
+        <v>2.52693052072201</v>
       </c>
       <c r="E11" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F11" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>47.04515319027373</v>
+        <v>7.644837393419482</v>
       </c>
       <c r="D12" t="n">
-        <v>18.28192151635067</v>
+        <v>2.970812246406985</v>
       </c>
       <c r="E12" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F12" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>45.28533036247822</v>
+        <v>7.358866183902711</v>
       </c>
       <c r="D13" t="n">
-        <v>45.28533036247822</v>
+        <v>7.358866183902711</v>
       </c>
       <c r="E13" t="n">
-        <v>10.83888857239919</v>
+        <v>1.761319393014868</v>
       </c>
       <c r="F13" t="n">
-        <v>7.867209222966698</v>
+        <v>1.278421498732089</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
